--- a/Codelist Excel Files and Conversion Templates to XML/gp_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/gp_properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10215"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A1471A-D69E-0143-8FEA-158E7F3B1DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875AF5D8-06AD-CF4B-94C2-F9E41B097972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="44820" windowHeight="27340" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="44820" windowHeight="27340" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="484">
   <si>
     <t>Description</t>
   </si>
@@ -641,9 +641,6 @@
     <t>thermodynamic temperature per thermodynamic temperature</t>
   </si>
   <si>
-    <t>unitless</t>
-  </si>
-  <si>
     <t>Leave this line blank</t>
   </si>
   <si>
@@ -1461,6 +1458,36 @@
   </si>
   <si>
     <t>volume or mass loss</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>Travel Time</t>
+  </si>
+  <si>
+    <t>Two-way Travel Time</t>
+  </si>
+  <si>
+    <t>the total elapsed time required for seismic energy (such as P-waves or S-waves) to propagate from a source (e.g., an earthquake focus or a seismic explosion) to a receiver (seismograph or geophone).</t>
+  </si>
+  <si>
+    <t>The total elapsed time it takes for a seismic wave or electromagnetic pulse to travel from a source (e.g., a seismic vibrator or air gun) down to a subsurface reflector or geological interface and return to a receiver (geophone or hydrophone) at the Earth's surface.</t>
+  </si>
+  <si>
+    <t>TWT</t>
+  </si>
+  <si>
+    <t>ancestor::diggs:measurement//diggs:procedure/diggs:GeophysicalProcessing/diggs:geophysicalMethod[text()="borehole crosshole seismic"]</t>
+  </si>
+  <si>
+    <t>ancestor::diggs:measurement//diggs:procedure/diggs:GeophysicalProcessing/diggs:geophysicalMethod[text()="borehole seismic downhole source"]</t>
+  </si>
+  <si>
+    <t>ancestor::diggs:measurement//diggs:procedure/diggs:GeophysicalProcessing/diggs:geophysicalMethod[text()="borehole seismic surface source"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> double</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1582,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1572,18 +1599,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBE5F1"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor theme="8" tint="0.59999389629810485"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor theme="8" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -1670,7 +1685,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1700,9 +1715,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1715,10 +1727,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1956,11 +1976,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H70" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:H70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H72" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A1:H72" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H72">
+    <sortCondition ref="F1:F72"/>
+  </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="12">
-      <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2940,1,FALSE)),"Not used","")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2938,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="11"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="10"/>
@@ -1975,14 +1998,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D136" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:D136" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D148" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D148" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D136">
     <sortCondition ref="D1:D136"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="3">
-      <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="1"/>
@@ -2293,7 +2316,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>14</v>
@@ -2308,21 +2331,21 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="102" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2337,7 +2360,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
@@ -2356,7 +2379,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>8</v>
@@ -2368,272 +2391,254 @@
         <v>165</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2940,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="E2" s="14" t="s">
+        <f>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2954,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>263</v>
       </c>
       <c r="G2" s="11"/>
     </row>
-    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B3,AssociatedElements!B$2:B2941,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="E3" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B3,AssociatedElements!B$2:B2947,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B4,AssociatedElements!B$2:B2942,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="E4" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B4,AssociatedElements!B$2:B2958,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B5,AssociatedElements!B$2:B2943,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B5,AssociatedElements!B$2:B2959,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2944,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="E6" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2967,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="E7" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2974,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2946,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2984,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B9,AssociatedElements!B$2:B2947,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="D9" s="17" t="s">
+        <f>IF(ISNA(VLOOKUP(B9,AssociatedElements!B$2:B2946,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="C9" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2948,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="E10" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="E10" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="E11" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2950,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2950,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>423</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="E12" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2951,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2951,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="E13" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2963,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -2643,19 +2648,19 @@
     </row>
     <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2952,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="E14" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2964,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -2665,19 +2670,19 @@
     </row>
     <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B15,AssociatedElements!B$2:B2953,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="E15" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B15,AssociatedElements!B$2:B2965,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -2687,437 +2692,437 @@
     </row>
     <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B16,AssociatedElements!B$2:B2954,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="E16" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B16,AssociatedElements!B$2:B2966,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B17,AssociatedElements!B$2:B2955,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="E17" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B17,AssociatedElements!B$2:B2975,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2956,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="E18" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2976,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>264</v>
+        <v>24</v>
       </c>
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2957,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="E19" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2977,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2958,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="E20" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2978,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>443</v>
+        <v>24</v>
       </c>
       <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2959,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="E21" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2979,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2960,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="E22" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2980,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="E22" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2961,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="E23" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2991,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="E24" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B3002,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2963,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="E25" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2985,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2964,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="E26" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2998,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2965,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="E27" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2999,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="E27" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G27" s="11"/>
     </row>
     <row r="28" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2966,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="E28" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B3000,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="E28" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G28" s="11"/>
     </row>
     <row r="29" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2967,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="E29" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2986,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G29" s="11"/>
     </row>
     <row r="30" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="E30" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2987,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G30" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2969,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="E31" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2983,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="E31" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G31" s="11"/>
     </row>
     <row r="32" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="E32" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2997,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G32" s="11"/>
     </row>
     <row r="33" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="E33" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2960,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="G33" s="11"/>
     </row>
     <row r="34" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="D34" s="17" t="s">
+        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="C34" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="E34" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="G34" s="11"/>
     </row>
     <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="D35" s="17" t="s">
+        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="C35" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F35" s="2" t="s">
@@ -3127,419 +3132,419 @@
     </row>
     <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2974,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="E36" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2956,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="E36" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>70</v>
+        <v>442</v>
       </c>
       <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2975,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="E37" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2942,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E37" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B38,AssociatedElements!B$2:B2976,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="E38" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B38,AssociatedElements!B$2:B2952,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G38" s="11"/>
     </row>
     <row r="39" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B39,AssociatedElements!B$2:B2977,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="E39" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B39,AssociatedElements!B$2:B2953,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G39" s="11"/>
     </row>
     <row r="40" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B40,AssociatedElements!B$2:B2978,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="C40" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="E40" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B40,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="E40" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B41,AssociatedElements!B$2:B2979,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>333</v>
-      </c>
-      <c r="E41" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B41,AssociatedElements!B$2:B2989,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="E41" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G41" s="11"/>
     </row>
     <row r="42" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B42,AssociatedElements!B$2:B2980,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="E42" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B42,AssociatedElements!B$2:B3001,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E42" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B43,AssociatedElements!B$2:B2981,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="E43" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B43,AssociatedElements!B$2:B2939,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="E43" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B44,AssociatedElements!B$2:B2982,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="E44" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B44,AssociatedElements!B$2:B2940,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="E44" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="G44" s="11"/>
     </row>
     <row r="45" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B45,AssociatedElements!B$2:B2983,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="E45" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B45,AssociatedElements!B$2:B2955,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="E45" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="G45" s="11"/>
     </row>
     <row r="46" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B46,AssociatedElements!B$2:B2984,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="E46" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B46,AssociatedElements!B$2:B2957,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E46" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="G46" s="11"/>
     </row>
     <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B47,AssociatedElements!B$2:B2985,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="E47" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B47,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="E47" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="G47" s="11"/>
     </row>
     <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B48,AssociatedElements!B$2:B2986,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>354</v>
-      </c>
-      <c r="E48" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B48,AssociatedElements!B$2:B2943,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="E48" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G48" s="11"/>
     </row>
     <row r="49" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B49,AssociatedElements!B$2:B2987,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>355</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="E49" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B49,AssociatedElements!B$2:B2948,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="E49" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="G49" s="11"/>
     </row>
     <row r="50" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B50,AssociatedElements!B$2:B2988,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="D50" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="E50" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B50,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="E50" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G50" s="11"/>
     </row>
     <row r="51" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B51,AssociatedElements!B$2:B2989,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="E51" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B51,AssociatedElements!B$2:B2969,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="E51" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G51" s="11"/>
     </row>
     <row r="52" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B52,AssociatedElements!B$2:B2990,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>366</v>
-      </c>
-      <c r="E52" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B52,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="E52" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G52" s="11"/>
     </row>
     <row r="53" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B53,AssociatedElements!B$2:B2991,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="E53" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B53,AssociatedElements!B$2:B2938,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" s="14" t="s">
         <v>1</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="G53" s="11"/>
     </row>
     <row r="54" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B54,AssociatedElements!B$2:B2992,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>370</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="E54" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B54,AssociatedElements!B$2:B2996,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="E54" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G54" s="11"/>
     </row>
@@ -3548,61 +3553,61 @@
         <f>IF(ISNA(VLOOKUP(B55,AssociatedElements!B$2:B2993,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B55" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="D55" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="E55" s="19" t="s">
+      <c r="B55" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="E55" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G55" s="11"/>
     </row>
     <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B56,AssociatedElements!B$2:B2994,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="D56" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="E56" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B56,AssociatedElements!B$2:B2995,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E56" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G56" s="11"/>
     </row>
     <row r="57" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B57,AssociatedElements!B$2:B2995,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>379</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="D57" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>1</v>
+      <c r="A57" s="21" t="str">
+        <f>IF(ISNA(VLOOKUP(B57,AssociatedElements!B$2:B2996,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>483</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>25</v>
@@ -3610,42 +3615,42 @@
       <c r="G57" s="11"/>
     </row>
     <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="str">
+      <c r="A58" s="21" t="str">
         <f>IF(ISNA(VLOOKUP(B58,AssociatedElements!B$2:B2996,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B58" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="C58" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="D58" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="E58" s="19" t="s">
+      <c r="B58" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="E58" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G58" s="11"/>
     </row>
     <row r="59" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B59,AssociatedElements!B$2:B2997,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>385</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="E59" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B59,AssociatedElements!B$2:B3006,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="E59" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F59" s="2" t="s">
@@ -3653,247 +3658,261 @@
       </c>
       <c r="G59" s="11"/>
     </row>
-    <row r="60" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B60,AssociatedElements!B$2:B2998,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>388</v>
+        <f>IF(ISNA(VLOOKUP(B60,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>234</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>389</v>
+        <v>235</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="E60" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="E60" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G60" s="11"/>
     </row>
-    <row r="61" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B61,AssociatedElements!B$2:B2999,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>391</v>
+        <f>IF(ISNA(VLOOKUP(B61,AssociatedElements!B$2:B2988,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>363</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>393</v>
-      </c>
-      <c r="E61" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="E61" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G61" s="11"/>
     </row>
     <row r="62" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B62,AssociatedElements!B$2:B3000,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>394</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>395</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="E62" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B62,AssociatedElements!B$2:B2990,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E62" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="G62" s="11"/>
     </row>
     <row r="63" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B63,AssociatedElements!B$2:B3001,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="D63" s="17" t="s">
-        <v>399</v>
-      </c>
-      <c r="E63" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B63,AssociatedElements!B$2:B2941,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="G63" s="11"/>
     </row>
     <row r="64" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B64,AssociatedElements!B$2:B3002,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="D64" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="E64" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B64,AssociatedElements!B$2:B2944,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="E64" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="G64" s="11"/>
     </row>
     <row r="65" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B65,AssociatedElements!B$2:B3003,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>403</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>404</v>
-      </c>
-      <c r="D65" s="17" t="s">
-        <v>405</v>
-      </c>
-      <c r="E65" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B65,AssociatedElements!B$2:B2961,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="E65" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="G65" s="11"/>
     </row>
     <row r="66" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B66,AssociatedElements!B$2:B3004,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B66" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="E66" s="19" t="s">
+        <f>IF(ISNA(VLOOKUP(B66,AssociatedElements!B$2:B2981,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="E66" s="18" t="s">
         <v>1</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G66" s="11"/>
     </row>
     <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B67,AssociatedElements!B$2:B3005,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>409</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>411</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>201</v>
+        <f>IF(ISNA(VLOOKUP(B67,AssociatedElements!B$2:B2982,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>1</v>
       </c>
       <c r="G67" s="11"/>
     </row>
     <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B68,AssociatedElements!B$2:B3006,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B68" s="16" t="s">
-        <v>412</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="D68" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>201</v>
+        <f>IF(ISNA(VLOOKUP(B68,AssociatedElements!B$2:B2992,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>1</v>
       </c>
       <c r="G68" s="11"/>
     </row>
     <row r="69" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B69,AssociatedElements!B$2:B3007,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B69" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="C69" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>417</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>201</v>
+        <f>IF(ISNA(VLOOKUP(B69,AssociatedElements!B$2:B2994,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>1</v>
       </c>
       <c r="G69" s="11"/>
     </row>
     <row r="70" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="str">
-        <f>IF(ISNA(VLOOKUP(B70,AssociatedElements!B$2:B3008,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>418</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>420</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>25</v>
+        <f>IF(ISNA(VLOOKUP(B70,AssociatedElements!B$2:B3003,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>180</v>
       </c>
       <c r="G70" s="11"/>
+    </row>
+    <row r="71" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="str">
+        <f>IF(ISNA(VLOOKUP(B71,AssociatedElements!B$2:B3004,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G71" s="11"/>
+    </row>
+    <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="str">
+        <f>IF(ISNA(VLOOKUP(B72,AssociatedElements!B$2:B3005,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3919,13 +3938,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" customWidth="1"/>
     <col min="3" max="3" width="86.1640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="93" customWidth="1"/>
+    <col min="4" max="4" width="127.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -3933,2038 +3952,2218 @@
         <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
-        <f>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
-        <f>IF(ISNA(VLOOKUP(B3,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B3,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <f>IF(ISNA(VLOOKUP(B4,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B4,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <f>IF(ISNA(VLOOKUP(B5,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B5,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <f>IF(ISNA(VLOOKUP(B6,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B6,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
-        <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D11" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D12" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <f>IF(ISNA(VLOOKUP(B13,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B13,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <f>IF(ISNA(VLOOKUP(B14,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B14,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <f>IF(ISNA(VLOOKUP(B15,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B15,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <f>IF(ISNA(VLOOKUP(B16,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B16,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D16" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <f>IF(ISNA(VLOOKUP(B17,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B17,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
-        <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B19" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D19" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D20" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B21" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D21" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <f>IF(ISNA(VLOOKUP(B22,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B22,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <f>IF(ISNA(VLOOKUP(B23,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B23,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B23" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B24" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B27" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D28" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D29" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D30" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D31" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B32" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D32" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B33" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D33" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B34" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D34" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D35" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D36" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <f>IF(ISNA(VLOOKUP(B37,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B37,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D37" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <f>IF(ISNA(VLOOKUP(B38,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B38,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B38" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D38" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <f>IF(ISNA(VLOOKUP(B39,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B39,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B39" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D39" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <f>IF(ISNA(VLOOKUP(B40,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B40,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D40" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
-        <f>IF(ISNA(VLOOKUP(B41,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B41,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D41" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="str">
-        <f>IF(ISNA(VLOOKUP(B42,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B42,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D42" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="str">
-        <f>IF(ISNA(VLOOKUP(B43,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B43,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D43" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="str">
-        <f>IF(ISNA(VLOOKUP(B44,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B44,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D44" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="str">
-        <f>IF(ISNA(VLOOKUP(B45,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B45,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B45" t="s">
         <v>42</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D45" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="str">
-        <f>IF(ISNA(VLOOKUP(B46,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B46,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B46" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D46" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="str">
-        <f>IF(ISNA(VLOOKUP(B47,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B47,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D47" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="str">
-        <f>IF(ISNA(VLOOKUP(B48,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B48,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B48" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D48" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="str">
-        <f>IF(ISNA(VLOOKUP(B49,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B49,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B49" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D49" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="str">
-        <f>IF(ISNA(VLOOKUP(B50,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B50,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D50" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="str">
-        <f>IF(ISNA(VLOOKUP(B51,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B51,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B51" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D51" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="str">
-        <f>IF(ISNA(VLOOKUP(B52,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B52,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B52" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D52" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="str">
-        <f>IF(ISNA(VLOOKUP(B53,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B53,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B53" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D53" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="str">
-        <f>IF(ISNA(VLOOKUP(B54,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B54,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B54" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D54" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="str">
-        <f>IF(ISNA(VLOOKUP(B55,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B55,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B55" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="str">
-        <f>IF(ISNA(VLOOKUP(B56,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B56,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B56" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D56" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="str">
-        <f>IF(ISNA(VLOOKUP(B57,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B57,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B57" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D57" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="str">
-        <f>IF(ISNA(VLOOKUP(B58,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B58,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B58" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D58" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="str">
-        <f>IF(ISNA(VLOOKUP(B59,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B59,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B59" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D59" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="str">
-        <f>IF(ISNA(VLOOKUP(B60,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B60,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B60" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D60" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="str">
-        <f>IF(ISNA(VLOOKUP(B61,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B61,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B61" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D61" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="str">
-        <f>IF(ISNA(VLOOKUP(B62,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B62,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D62" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="str">
-        <f>IF(ISNA(VLOOKUP(B63,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B63,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D63" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="str">
-        <f>IF(ISNA(VLOOKUP(B64,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B64,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B64" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="str">
-        <f>IF(ISNA(VLOOKUP(B65,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B65,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B65" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D65" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="str">
-        <f>IF(ISNA(VLOOKUP(B66,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B66,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B66" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D66" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="str">
-        <f>IF(ISNA(VLOOKUP(B67,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B67,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B67" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D67" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="str">
-        <f>IF(ISNA(VLOOKUP(B68,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B68,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B68" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D68" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="str">
-        <f>IF(ISNA(VLOOKUP(B69,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B69,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D69" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="str">
-        <f>IF(ISNA(VLOOKUP(B70,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B70,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B70" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D70" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="str">
-        <f>IF(ISNA(VLOOKUP(B71,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B71,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B71" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D71" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="str">
-        <f>IF(ISNA(VLOOKUP(B72,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B72,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B72" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="str">
-        <f>IF(ISNA(VLOOKUP(B73,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B73,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B73" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D73" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="str">
-        <f>IF(ISNA(VLOOKUP(B74,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B74,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B74" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D74" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="str">
-        <f>IF(ISNA(VLOOKUP(B75,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B75,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D75" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="str">
-        <f>IF(ISNA(VLOOKUP(B76,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B76,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B76" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D76" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="str">
-        <f>IF(ISNA(VLOOKUP(B77,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B77,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B77" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D77" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="str">
-        <f>IF(ISNA(VLOOKUP(B78,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B78,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B78" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D78" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="str">
-        <f>IF(ISNA(VLOOKUP(B79,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B79,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B79" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D79" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="str">
-        <f>IF(ISNA(VLOOKUP(B80,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B80,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B80" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D80" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="str">
-        <f>IF(ISNA(VLOOKUP(B81,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B81,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B81" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D81" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="str">
-        <f>IF(ISNA(VLOOKUP(B82,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B82,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B82" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D82" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="str">
-        <f>IF(ISNA(VLOOKUP(B83,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B83,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B83" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D83" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="str">
-        <f>IF(ISNA(VLOOKUP(B84,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B84,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D84" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="str">
-        <f>IF(ISNA(VLOOKUP(B85,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B85,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B85" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D85" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="str">
-        <f>IF(ISNA(VLOOKUP(B86,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B86,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="str">
-        <f>IF(ISNA(VLOOKUP(B87,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B87,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B87" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D87" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="str">
-        <f>IF(ISNA(VLOOKUP(B88,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B88,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B88" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D88" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="str">
-        <f>IF(ISNA(VLOOKUP(B89,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B89,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B89" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D89" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="str">
-        <f>IF(ISNA(VLOOKUP(B90,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B90,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B90" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D90" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="str">
-        <f>IF(ISNA(VLOOKUP(B91,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B91,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B91" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D91" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="str">
-        <f>IF(ISNA(VLOOKUP(B92,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B92,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B92" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D92" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="str">
-        <f>IF(ISNA(VLOOKUP(B93,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B93,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B93" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D93" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="str">
-        <f>IF(ISNA(VLOOKUP(B94,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B94,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B94" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D94" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="str">
-        <f>IF(ISNA(VLOOKUP(B95,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B95,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B95" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D95" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="str">
-        <f>IF(ISNA(VLOOKUP(B96,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B96,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B96" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D96" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="str">
-        <f>IF(ISNA(VLOOKUP(B97,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B97,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B97" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D97" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="str">
-        <f>IF(ISNA(VLOOKUP(B98,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B98,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B98" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D98" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="str">
-        <f>IF(ISNA(VLOOKUP(B99,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B99,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B99" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D99" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="str">
-        <f>IF(ISNA(VLOOKUP(B100,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B100,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B100" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D100" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="str">
-        <f>IF(ISNA(VLOOKUP(B101,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B101,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B101" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D101" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="str">
-        <f>IF(ISNA(VLOOKUP(B102,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B102,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B102" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D102" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="str">
-        <f>IF(ISNA(VLOOKUP(B103,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B103,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B103" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D103" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="str">
-        <f>IF(ISNA(VLOOKUP(B104,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B104,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B104" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D104" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="str">
-        <f>IF(ISNA(VLOOKUP(B105,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B105,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B105" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D105" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="str">
-        <f>IF(ISNA(VLOOKUP(B106,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B106,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B106" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D106" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="str">
-        <f>IF(ISNA(VLOOKUP(B107,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B107,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B107" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D107" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="str">
-        <f>IF(ISNA(VLOOKUP(B108,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B108,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B108" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D108" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="str">
-        <f>IF(ISNA(VLOOKUP(B109,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B109,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B109" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D109" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="str">
-        <f>IF(ISNA(VLOOKUP(B110,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B110,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B110" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D110" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="str">
-        <f>IF(ISNA(VLOOKUP(B111,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B111,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B111" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D111" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="str">
-        <f>IF(ISNA(VLOOKUP(B112,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B112,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B112" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D112" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="str">
-        <f>IF(ISNA(VLOOKUP(B113,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B113,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B113" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D113" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="str">
-        <f>IF(ISNA(VLOOKUP(B114,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B114,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B114" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D114" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="str">
-        <f>IF(ISNA(VLOOKUP(B115,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B115,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B115" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D115" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="str">
-        <f>IF(ISNA(VLOOKUP(B116,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B116,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B116" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D116" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="str">
-        <f>IF(ISNA(VLOOKUP(B117,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B117,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B117" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D117" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A118" t="str">
-        <f>IF(ISNA(VLOOKUP(B118,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B118,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B118" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D118" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A119" t="str">
-        <f>IF(ISNA(VLOOKUP(B119,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B119,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B119" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D119" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A120" t="str">
-        <f>IF(ISNA(VLOOKUP(B120,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B120,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B120" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D120" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A121" t="str">
-        <f>IF(ISNA(VLOOKUP(B121,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B121,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B121" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D121" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A122" t="str">
-        <f>IF(ISNA(VLOOKUP(B122,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B122,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B122" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D122" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A123" t="str">
-        <f>IF(ISNA(VLOOKUP(B123,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B123,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B123" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D123" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A124" t="str">
-        <f>IF(ISNA(VLOOKUP(B124,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B124,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B124" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D124" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A125" t="str">
-        <f>IF(ISNA(VLOOKUP(B125,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B125,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B125" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D125" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A126" t="str">
-        <f>IF(ISNA(VLOOKUP(B126,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B126,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B126" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D126" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A127" t="str">
-        <f>IF(ISNA(VLOOKUP(B127,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B127,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B127" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D127" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A128" t="str">
-        <f>IF(ISNA(VLOOKUP(B128,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B128,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B128" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D128" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A129" t="str">
-        <f>IF(ISNA(VLOOKUP(B129,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B129,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B129" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D129" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A130" t="str">
-        <f>IF(ISNA(VLOOKUP(B130,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B130,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B130" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D130" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A131" t="str">
-        <f>IF(ISNA(VLOOKUP(B131,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B131,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B131" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D131" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A132" t="str">
-        <f>IF(ISNA(VLOOKUP(B132,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B132,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B132" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D132" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A133" t="str">
-        <f>IF(ISNA(VLOOKUP(B133,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B133,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B133" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D133" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A134" t="str">
-        <f>IF(ISNA(VLOOKUP(B134,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B134,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B134" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D134" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A135" t="str">
-        <f>IF(ISNA(VLOOKUP(B135,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B135,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B135" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D135" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A136" t="str">
-        <f>IF(ISNA(VLOOKUP(B136,Definitions!B$2:B$1880,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B136,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B136" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D136" t="s">
-        <v>425</v>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A137" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B137,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B137" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D137" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A138" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B138,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B138" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D138" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A139" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B139,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B139" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D139" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A140" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B140,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B140" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D140" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A141" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B141,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B141" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D141" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A142" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B142,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B142" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D142" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A143" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B143,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B143" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D143" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A144" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B144,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B144" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D144" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A145" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B145,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B145" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D145" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A146" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B146,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B146" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D146" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A147" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B147,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B147" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D147" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A148" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B148,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B148" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D148" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -5995,16 +6194,16 @@
         <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -6019,7 +6218,7 @@
         <v>absorbed dose</v>
       </c>
       <c r="M2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -6027,14 +6226,14 @@
         <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D3" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>activity [of radioactivity]</v>
       </c>
       <c r="M3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -6049,7 +6248,7 @@
         <v>amount of substance</v>
       </c>
       <c r="M4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -6064,7 +6263,7 @@
         <v>amount of substance per amount of substance</v>
       </c>
       <c r="M5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -6079,7 +6278,7 @@
         <v>amount of substance per area</v>
       </c>
       <c r="M6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -6087,17 +6286,17 @@
         <v>167</v>
       </c>
       <c r="C7" t="s">
+        <v>445</v>
+      </c>
+      <c r="D7" s="7" t="e">
+        <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E7" t="s">
         <v>446</v>
       </c>
-      <c r="D7" s="7" t="e">
-        <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E7" t="s">
-        <v>447</v>
-      </c>
       <c r="M7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -6112,7 +6311,7 @@
         <v>amount of substance per time</v>
       </c>
       <c r="M8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -6120,14 +6319,14 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D9" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>(amount of substance per time) per area</v>
       </c>
       <c r="M9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -6142,7 +6341,7 @@
         <v>amount of substance per volume</v>
       </c>
       <c r="M10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -6157,7 +6356,7 @@
         <v>angle per length</v>
       </c>
       <c r="M11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -6172,7 +6371,7 @@
         <v>angle per volume</v>
       </c>
       <c r="M12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -6202,7 +6401,7 @@
         <v>angular velocity</v>
       </c>
       <c r="M14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -6267,7 +6466,7 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C19" t="s">
         <v>37</v>
@@ -6307,7 +6506,7 @@
         <v>#N/A</v>
       </c>
       <c r="E21" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M21" t="s">
         <v>33</v>
@@ -6355,7 +6554,7 @@
         <v>area per volume</v>
       </c>
       <c r="M24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.2">
@@ -6370,7 +6569,7 @@
         <v>attenuation per frequency interval</v>
       </c>
       <c r="M25" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.2">
@@ -6385,7 +6584,7 @@
         <v>capacitance</v>
       </c>
       <c r="M26" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.2">
@@ -6430,7 +6629,7 @@
         <v>#N/A</v>
       </c>
       <c r="E29" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M29" t="s">
         <v>38</v>
@@ -6513,7 +6712,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C35" t="s">
         <v>49</v>
@@ -6756,7 +6955,7 @@
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D55" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -6816,14 +7015,14 @@
     </row>
     <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D60" s="7" t="e">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E60" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M60" t="s">
         <v>64</v>
@@ -6891,14 +7090,14 @@
     </row>
     <row r="66" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C66" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D66" s="7" t="e">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E66" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="M66" t="s">
         <v>18</v>
@@ -7350,7 +7549,7 @@
     </row>
     <row r="104" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C104" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D104" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -7362,7 +7561,7 @@
     </row>
     <row r="105" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C105" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D105" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -7386,7 +7585,7 @@
     </row>
     <row r="107" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C107" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D107" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -7398,14 +7597,14 @@
     </row>
     <row r="108" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C108" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D108" s="7" t="e">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E108" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M108" t="s">
         <v>17</v>
@@ -7413,14 +7612,14 @@
     </row>
     <row r="109" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C109" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D109" s="7" t="e">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E109" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M109" t="s">
         <v>106</v>
@@ -7663,7 +7862,7 @@
         <v>#N/A</v>
       </c>
       <c r="E129" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M129" t="s">
         <v>124</v>
@@ -7690,7 +7889,7 @@
         <v>pressure per volume</v>
       </c>
       <c r="M131" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="132" spans="3:13" x14ac:dyDescent="0.2">
@@ -7707,7 +7906,7 @@
     </row>
     <row r="133" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C133" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D133" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -7750,7 +7949,7 @@
         <v>radiance</v>
       </c>
       <c r="M136" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="137" spans="3:13" x14ac:dyDescent="0.2">
@@ -7827,7 +8026,7 @@
     </row>
     <row r="143" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C143" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D143" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -7875,14 +8074,14 @@
     </row>
     <row r="147" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C147" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D147" s="7" t="e">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E147" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M147" t="s">
         <v>140</v>
@@ -8077,7 +8276,7 @@
         <v>#N/A</v>
       </c>
       <c r="E163" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M163" t="s">
         <v>153</v>
@@ -8238,7 +8437,7 @@
     </row>
     <row r="177" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C177" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D177" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -8247,7 +8446,7 @@
     </row>
     <row r="178" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C178" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D178" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -8256,7 +8455,7 @@
     </row>
     <row r="179" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C179" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D179" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -8265,7 +8464,7 @@
     </row>
     <row r="180" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C180" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D180" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -8274,7 +8473,7 @@
     </row>
     <row r="181" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C181" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D181" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -8283,7 +8482,7 @@
     </row>
     <row r="182" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C182" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D182" s="7" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -8292,7 +8491,7 @@
     </row>
     <row r="183" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C183" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D183" s="8" t="str">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
@@ -8328,87 +8527,63 @@
     </row>
     <row r="187" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C187" t="s">
-        <v>468</v>
-      </c>
-      <c r="D187" s="23" t="e">
+        <v>467</v>
+      </c>
+      <c r="D187" t="e">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E187" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="188" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C188" t="s">
-        <v>474</v>
-      </c>
-      <c r="D188" s="23" t="e">
+        <v>473</v>
+      </c>
+      <c r="D188" t="e">
         <f>VLOOKUP(Table6[[#This Row],[QuantityClass]],M$1:M$175,1,FALSE)</f>
         <v>#N/A</v>
       </c>
       <c r="E188" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="192" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="E192" s="20" t="s">
-        <v>471</v>
-      </c>
+      <c r="E192" s="19"/>
     </row>
     <row r="193" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E193" s="22" t="s">
-        <v>472</v>
-      </c>
+      <c r="E193" s="20"/>
     </row>
     <row r="194" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E194" s="21" t="s">
-        <v>446</v>
-      </c>
+      <c r="E194" s="19"/>
     </row>
     <row r="195" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E195" s="21" t="s">
-        <v>198</v>
-      </c>
+      <c r="E195" s="19"/>
     </row>
     <row r="196" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E196" s="20" t="s">
-        <v>199</v>
-      </c>
+      <c r="E196" s="19"/>
     </row>
     <row r="197" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E197" s="20" t="s">
-        <v>445</v>
-      </c>
+      <c r="E197" s="19"/>
     </row>
     <row r="198" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E198" s="20" t="s">
-        <v>443</v>
-      </c>
+      <c r="E198" s="19"/>
     </row>
     <row r="199" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E199" s="21" t="s">
-        <v>197</v>
-      </c>
+      <c r="E199" s="19"/>
     </row>
     <row r="200" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E200" s="21" t="s">
-        <v>468</v>
-      </c>
+      <c r="E200" s="19"/>
     </row>
     <row r="201" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E201" s="21" t="s">
-        <v>444</v>
-      </c>
+      <c r="E201" s="19"/>
     </row>
     <row r="202" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E202" s="21" t="s">
-        <v>200</v>
-      </c>
+      <c r="E202" s="19"/>
     </row>
     <row r="203" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E203" s="20" t="s">
-        <v>474</v>
-      </c>
+      <c r="E203" s="19"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E192:E203">

--- a/Codelist Excel Files and Conversion Templates to XML/gp_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/gp_properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875AF5D8-06AD-CF4B-94C2-F9E41B097972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5638A60B-A34F-B243-9F09-48827BFEA82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="44820" windowHeight="27340" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="44820" windowHeight="26600" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="486">
   <si>
     <t>Description</t>
   </si>
@@ -1488,6 +1488,12 @@
   </si>
   <si>
     <t xml:space="preserve"> double</t>
+  </si>
+  <si>
+    <t>//diggs:geoUnitType</t>
+  </si>
+  <si>
+    <t>//diggs:parameterName</t>
   </si>
 </sst>
 </file>
@@ -1727,18 +1733,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1809,6 +1813,42 @@
         <vertAlign val="baseline"/>
         <color theme="0"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1912,42 +1952,6 @@
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1962,46 +1966,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H72" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H72" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:H72" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H72">
     <sortCondition ref="F1:F72"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="19">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2938,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D148" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:D148" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D136">
-    <sortCondition ref="D1:D136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D151" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D151" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D150">
+    <sortCondition ref="B1:B150"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="3">
@@ -3240,7 +3244,7 @@
       </c>
       <c r="G40" s="11"/>
     </row>
-    <row r="41" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B41,AssociatedElements!B$2:B2989,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3306,7 +3310,7 @@
       </c>
       <c r="G43" s="11"/>
     </row>
-    <row r="44" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B44,AssociatedElements!B$2:B2940,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3372,7 +3376,7 @@
       </c>
       <c r="G46" s="11"/>
     </row>
-    <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B47,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3394,7 +3398,7 @@
       </c>
       <c r="G47" s="11"/>
     </row>
-    <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B48,AssociatedElements!B$2:B2943,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3416,7 +3420,7 @@
       </c>
       <c r="G48" s="11"/>
     </row>
-    <row r="49" spans="1:7" ht="85" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B49,AssociatedElements!B$2:B2948,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3438,7 +3442,7 @@
       </c>
       <c r="G49" s="11"/>
     </row>
-    <row r="50" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B50,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3482,7 +3486,7 @@
       </c>
       <c r="G51" s="11"/>
     </row>
-    <row r="52" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B52,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3504,7 +3508,7 @@
       </c>
       <c r="G52" s="11"/>
     </row>
-    <row r="53" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B53,AssociatedElements!B$2:B2938,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3512,10 +3516,10 @@
       <c r="B53" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C53" s="24" t="s">
+      <c r="C53" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="D53" s="24" t="s">
+      <c r="D53" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E53" s="14" t="s">
@@ -3526,7 +3530,7 @@
       </c>
       <c r="G53" s="11"/>
     </row>
-    <row r="54" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B54,AssociatedElements!B$2:B2996,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3548,7 +3552,7 @@
       </c>
       <c r="G54" s="11"/>
     </row>
-    <row r="55" spans="1:7" ht="85" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B55,AssociatedElements!B$2:B2993,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3570,7 +3574,7 @@
       </c>
       <c r="G55" s="11"/>
     </row>
-    <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B56,AssociatedElements!B$2:B2995,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3592,8 +3596,8 @@
       </c>
       <c r="G56" s="11"/>
     </row>
-    <row r="57" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A57" s="21" t="str">
+    <row r="57" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B57,AssociatedElements!B$2:B2996,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -3614,8 +3618,8 @@
       </c>
       <c r="G57" s="11"/>
     </row>
-    <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A58" s="21" t="str">
+    <row r="58" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B58,AssociatedElements!B$2:B2996,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="G58" s="11"/>
     </row>
-    <row r="59" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B59,AssociatedElements!B$2:B3006,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3658,7 +3662,7 @@
       </c>
       <c r="G59" s="11"/>
     </row>
-    <row r="60" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B60,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3702,7 +3706,7 @@
       </c>
       <c r="G61" s="11"/>
     </row>
-    <row r="62" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B62,AssociatedElements!B$2:B2990,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3781,7 +3785,7 @@
       </c>
       <c r="G65" s="11"/>
     </row>
-    <row r="66" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B66,AssociatedElements!B$2:B2981,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3800,7 +3804,7 @@
       </c>
       <c r="G66" s="11"/>
     </row>
-    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B67,AssociatedElements!B$2:B2982,1,FALSE)),"Not used","")</f>
         <v/>
@@ -3938,7 +3942,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
@@ -3967,13 +3971,13 @@
         <v/>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D2" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3982,13 +3986,13 @@
         <v/>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D3" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3997,13 +4001,13 @@
         <v/>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D4" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4012,13 +4016,13 @@
         <v/>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D5" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4027,7 +4031,7 @@
         <v/>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>421</v>
@@ -4042,13 +4046,13 @@
         <v/>
       </c>
       <c r="B7" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D7" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4057,13 +4061,13 @@
         <v/>
       </c>
       <c r="B8" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D8" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4072,13 +4076,13 @@
         <v/>
       </c>
       <c r="B9" t="s">
-        <v>300</v>
+        <v>223</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D9" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4087,28 +4091,28 @@
         <v/>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>223</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D10" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" t="s">
-        <v>321</v>
+      <c r="B11" s="10" t="s">
+        <v>223</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4117,7 +4121,7 @@
         <v/>
       </c>
       <c r="B12" t="s">
-        <v>354</v>
+        <v>226</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>421</v>
@@ -4126,19 +4130,19 @@
         <v>423</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>IF(ISNA(VLOOKUP(B13,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B13" t="s">
-        <v>357</v>
+      <c r="B13" s="10" t="s">
+        <v>226</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4147,7 +4151,7 @@
         <v/>
       </c>
       <c r="B14" t="s">
-        <v>363</v>
+        <v>229</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>421</v>
@@ -4162,13 +4166,13 @@
         <v/>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>229</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D15" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -4177,13 +4181,13 @@
         <v/>
       </c>
       <c r="B16" t="s">
-        <v>369</v>
+        <v>229</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D16" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4192,28 +4196,28 @@
         <v/>
       </c>
       <c r="B17" t="s">
-        <v>372</v>
+        <v>229</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D17" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B18" t="s">
-        <v>387</v>
+      <c r="B18" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4222,13 +4226,13 @@
         <v/>
       </c>
       <c r="B19" t="s">
-        <v>390</v>
+        <v>42</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D19" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -4237,7 +4241,7 @@
         <v/>
       </c>
       <c r="B20" t="s">
-        <v>402</v>
+        <v>234</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>421</v>
@@ -4246,19 +4250,19 @@
         <v>423</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B21" t="s">
-        <v>405</v>
+      <c r="B21" s="10" t="s">
+        <v>234</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -4267,13 +4271,13 @@
         <v/>
       </c>
       <c r="B22" t="s">
-        <v>408</v>
+        <v>237</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D22" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4282,13 +4286,13 @@
         <v/>
       </c>
       <c r="B23" t="s">
-        <v>411</v>
+        <v>237</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D23" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4297,13 +4301,13 @@
         <v/>
       </c>
       <c r="B24" t="s">
-        <v>414</v>
+        <v>237</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D24" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4312,28 +4316,28 @@
         <v/>
       </c>
       <c r="B25" t="s">
-        <v>417</v>
+        <v>237</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D25" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B26" t="s">
-        <v>327</v>
+      <c r="B26" s="10" t="s">
+        <v>237</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D26" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4342,13 +4346,13 @@
         <v/>
       </c>
       <c r="B27" t="s">
-        <v>357</v>
+        <v>240</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D27" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4357,13 +4361,13 @@
         <v/>
       </c>
       <c r="B28" t="s">
-        <v>360</v>
+        <v>243</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D28" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4372,13 +4376,13 @@
         <v/>
       </c>
       <c r="B29" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D29" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4387,13 +4391,13 @@
         <v/>
       </c>
       <c r="B30" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D30" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4402,13 +4406,13 @@
         <v/>
       </c>
       <c r="B31" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D31" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4417,13 +4421,13 @@
         <v/>
       </c>
       <c r="B32" t="s">
-        <v>342</v>
+        <v>248</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D32" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4432,13 +4436,13 @@
         <v/>
       </c>
       <c r="B33" t="s">
-        <v>345</v>
+        <v>251</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D33" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4447,13 +4451,13 @@
         <v/>
       </c>
       <c r="B34" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D34" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4462,13 +4466,13 @@
         <v/>
       </c>
       <c r="B35" t="s">
-        <v>217</v>
+        <v>327</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D35" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -4477,13 +4481,13 @@
         <v/>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>324</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D36" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4492,13 +4496,13 @@
         <v/>
       </c>
       <c r="B37" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D37" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4507,28 +4511,28 @@
         <v/>
       </c>
       <c r="B38" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D38" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
         <f>IF(ISNA(VLOOKUP(B39,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B39" t="s">
-        <v>267</v>
+      <c r="B39" s="10" t="s">
+        <v>257</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D39" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4537,28 +4541,28 @@
         <v/>
       </c>
       <c r="B40" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D40" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
         <f>IF(ISNA(VLOOKUP(B41,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B41" t="s">
-        <v>237</v>
+      <c r="B41" s="10" t="s">
+        <v>260</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D41" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4567,13 +4571,13 @@
         <v/>
       </c>
       <c r="B42" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D42" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4582,13 +4586,13 @@
         <v/>
       </c>
       <c r="B43" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D43" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4597,13 +4601,13 @@
         <v/>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D44" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4612,13 +4616,13 @@
         <v/>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>273</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D45" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4627,13 +4631,13 @@
         <v/>
       </c>
       <c r="B46" t="s">
-        <v>360</v>
+        <v>273</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D46" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4642,13 +4646,13 @@
         <v/>
       </c>
       <c r="B47" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D47" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4657,13 +4661,13 @@
         <v/>
       </c>
       <c r="B48" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D48" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4672,13 +4676,13 @@
         <v/>
       </c>
       <c r="B49" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D49" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4687,13 +4691,13 @@
         <v/>
       </c>
       <c r="B50" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D50" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4702,13 +4706,13 @@
         <v/>
       </c>
       <c r="B51" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D51" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4717,13 +4721,13 @@
         <v/>
       </c>
       <c r="B52" t="s">
-        <v>357</v>
+        <v>285</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D52" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4732,13 +4736,13 @@
         <v/>
       </c>
       <c r="B53" t="s">
-        <v>360</v>
+        <v>288</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D53" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4747,7 +4751,7 @@
         <v/>
       </c>
       <c r="B54" t="s">
-        <v>393</v>
+        <v>291</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>421</v>
@@ -4762,13 +4766,13 @@
         <v/>
       </c>
       <c r="B55" t="s">
-        <v>396</v>
+        <v>291</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D55" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -4777,7 +4781,7 @@
         <v/>
       </c>
       <c r="B56" t="s">
-        <v>399</v>
+        <v>294</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>421</v>
@@ -4792,7 +4796,7 @@
         <v/>
       </c>
       <c r="B57" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>421</v>
@@ -4807,13 +4811,13 @@
         <v/>
       </c>
       <c r="B58" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D58" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4822,7 +4826,7 @@
         <v/>
       </c>
       <c r="B59" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>421</v>
@@ -4837,13 +4841,13 @@
         <v/>
       </c>
       <c r="B60" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D60" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4852,7 +4856,7 @@
         <v/>
       </c>
       <c r="B61" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>421</v>
@@ -4861,19 +4865,19 @@
         <v>432</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" t="str">
         <f>IF(ISNA(VLOOKUP(B62,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="10" t="s">
         <v>300</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D62" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4882,13 +4886,13 @@
         <v/>
       </c>
       <c r="B63" t="s">
-        <v>223</v>
+        <v>333</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D63" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4912,13 +4916,13 @@
         <v/>
       </c>
       <c r="B65" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D65" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -4927,13 +4931,13 @@
         <v/>
       </c>
       <c r="B66" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D66" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -4942,13 +4946,13 @@
         <v/>
       </c>
       <c r="B67" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D67" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -4957,7 +4961,7 @@
         <v/>
       </c>
       <c r="B68" t="s">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>421</v>
@@ -4972,7 +4976,7 @@
         <v/>
       </c>
       <c r="B69" t="s">
-        <v>223</v>
+        <v>306</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>421</v>
@@ -4987,13 +4991,13 @@
         <v/>
       </c>
       <c r="B70" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D70" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -5008,7 +5012,7 @@
         <v>421</v>
       </c>
       <c r="D71" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -5017,13 +5021,13 @@
         <v/>
       </c>
       <c r="B72" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D72" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -5032,13 +5036,13 @@
         <v/>
       </c>
       <c r="B73" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D73" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -5047,13 +5051,13 @@
         <v/>
       </c>
       <c r="B74" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D74" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -5062,13 +5066,13 @@
         <v/>
       </c>
       <c r="B75" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D75" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -5077,13 +5081,13 @@
         <v/>
       </c>
       <c r="B76" t="s">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D76" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -5092,13 +5096,13 @@
         <v/>
       </c>
       <c r="B77" t="s">
-        <v>375</v>
+        <v>318</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D77" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -5107,13 +5111,13 @@
         <v/>
       </c>
       <c r="B78" t="s">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D78" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -5122,13 +5126,13 @@
         <v/>
       </c>
       <c r="B79" t="s">
-        <v>381</v>
+        <v>318</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D79" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -5137,13 +5141,13 @@
         <v/>
       </c>
       <c r="B80" t="s">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D80" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -5152,28 +5156,28 @@
         <v/>
       </c>
       <c r="B81" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D81" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A82" t="str">
         <f>IF(ISNA(VLOOKUP(B82,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B82" t="s">
-        <v>315</v>
+      <c r="B82" s="10" t="s">
+        <v>318</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D82" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -5182,13 +5186,13 @@
         <v/>
       </c>
       <c r="B83" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D83" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -5197,13 +5201,13 @@
         <v/>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>321</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D84" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -5212,13 +5216,13 @@
         <v/>
       </c>
       <c r="B85" t="s">
-        <v>223</v>
+        <v>321</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D85" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
@@ -5227,7 +5231,7 @@
         <v/>
       </c>
       <c r="B86" t="s">
-        <v>229</v>
+        <v>321</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>421</v>
@@ -5242,28 +5246,28 @@
         <v/>
       </c>
       <c r="B87" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D87" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A88" t="str">
         <f>IF(ISNA(VLOOKUP(B88,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B88" t="s">
-        <v>306</v>
+      <c r="B88" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D88" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
@@ -5272,13 +5276,13 @@
         <v/>
       </c>
       <c r="B89" t="s">
-        <v>309</v>
+        <v>342</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D89" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
@@ -5287,13 +5291,13 @@
         <v/>
       </c>
       <c r="B90" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D90" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -5302,13 +5306,13 @@
         <v/>
       </c>
       <c r="B91" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D91" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
@@ -5317,13 +5321,13 @@
         <v/>
       </c>
       <c r="B92" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D92" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
@@ -5332,7 +5336,7 @@
         <v/>
       </c>
       <c r="B93" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>421</v>
@@ -5347,28 +5351,28 @@
         <v/>
       </c>
       <c r="B94" t="s">
-        <v>214</v>
+        <v>354</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D94" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A95" t="str">
         <f>IF(ISNA(VLOOKUP(B95,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B95" t="s">
-        <v>223</v>
+      <c r="B95" s="10" t="s">
+        <v>354</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D95" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
@@ -5377,13 +5381,13 @@
         <v/>
       </c>
       <c r="B96" t="s">
-        <v>229</v>
+        <v>357</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D96" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
@@ -5392,13 +5396,13 @@
         <v/>
       </c>
       <c r="B97" t="s">
-        <v>303</v>
+        <v>357</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D97" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
@@ -5407,13 +5411,13 @@
         <v/>
       </c>
       <c r="B98" t="s">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D98" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
@@ -5422,13 +5426,13 @@
         <v/>
       </c>
       <c r="B99" t="s">
-        <v>309</v>
+        <v>357</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D99" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
@@ -5437,28 +5441,28 @@
         <v/>
       </c>
       <c r="B100" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D100" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A101" t="str">
         <f>IF(ISNA(VLOOKUP(B101,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B101" t="s">
-        <v>321</v>
+      <c r="B101" s="10" t="s">
+        <v>357</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D101" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
@@ -5467,13 +5471,13 @@
         <v/>
       </c>
       <c r="B102" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D102" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
@@ -5482,13 +5486,13 @@
         <v/>
       </c>
       <c r="B103" t="s">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D103" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
@@ -5497,13 +5501,13 @@
         <v/>
       </c>
       <c r="B104" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D104" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
@@ -5512,13 +5516,13 @@
         <v/>
       </c>
       <c r="B105" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D105" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
@@ -5527,13 +5531,13 @@
         <v/>
       </c>
       <c r="B106" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D106" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
@@ -5542,28 +5546,28 @@
         <v/>
       </c>
       <c r="B107" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D107" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A108" t="str">
         <f>IF(ISNA(VLOOKUP(B108,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B108" t="s">
-        <v>339</v>
+      <c r="B108" s="10" t="s">
+        <v>363</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D108" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
@@ -5572,13 +5576,13 @@
         <v/>
       </c>
       <c r="B109" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D109" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
@@ -5587,13 +5591,13 @@
         <v/>
       </c>
       <c r="B110" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D110" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
@@ -5602,13 +5606,13 @@
         <v/>
       </c>
       <c r="B111" t="s">
-        <v>237</v>
+        <v>366</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D111" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
@@ -5617,13 +5621,13 @@
         <v/>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>366</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D112" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
@@ -5632,58 +5636,52 @@
         <v/>
       </c>
       <c r="B113" t="s">
-        <v>248</v>
+        <v>366</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D113" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A114" t="str">
         <f>IF(ISNA(VLOOKUP(B114,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B114" t="s">
-        <v>251</v>
+      <c r="B114" s="10" t="s">
+        <v>366</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D114" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" t="str">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A115" s="22" t="str">
         <f>IF(ISNA(VLOOKUP(B115,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B115" t="s">
-        <v>273</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D115" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" t="str">
+      <c r="B115" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="C115" s="24" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A116" s="22" t="str">
         <f>IF(ISNA(VLOOKUP(B116,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B116" t="s">
-        <v>276</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D116" t="s">
-        <v>441</v>
+      <c r="B116" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="C116" s="24" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
@@ -5692,13 +5690,13 @@
         <v/>
       </c>
       <c r="B117" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D117" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5707,7 +5705,7 @@
         <v/>
       </c>
       <c r="B118" s="10" t="s">
-        <v>223</v>
+        <v>369</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>421</v>
@@ -5716,19 +5714,19 @@
         <v>424</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="str">
         <f>IF(ISNA(VLOOKUP(B119,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B119" s="10" t="s">
-        <v>226</v>
+      <c r="B119" t="s">
+        <v>372</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D119" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5737,7 +5735,7 @@
         <v/>
       </c>
       <c r="B120" s="10" t="s">
-        <v>229</v>
+        <v>372</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>421</v>
@@ -5746,79 +5744,79 @@
         <v>424</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="str">
         <f>IF(ISNA(VLOOKUP(B121,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B121" s="10" t="s">
-        <v>234</v>
+      <c r="B121" t="s">
+        <v>375</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D121" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="str">
         <f>IF(ISNA(VLOOKUP(B122,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B122" s="10" t="s">
-        <v>237</v>
+      <c r="B122" t="s">
+        <v>378</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D122" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="str">
         <f>IF(ISNA(VLOOKUP(B123,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B123" s="10" t="s">
-        <v>257</v>
+      <c r="B123" t="s">
+        <v>381</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D123" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="str">
         <f>IF(ISNA(VLOOKUP(B124,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B124" s="10" t="s">
-        <v>260</v>
+      <c r="B124" t="s">
+        <v>384</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D124" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="str">
         <f>IF(ISNA(VLOOKUP(B125,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B125" s="10" t="s">
-        <v>300</v>
+      <c r="B125" t="s">
+        <v>387</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D125" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5827,7 +5825,7 @@
         <v/>
       </c>
       <c r="B126" s="10" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>421</v>
@@ -5836,19 +5834,19 @@
         <v>424</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="str">
         <f>IF(ISNA(VLOOKUP(B127,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B127" s="10" t="s">
-        <v>321</v>
+      <c r="B127" t="s">
+        <v>390</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D127" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5857,7 +5855,7 @@
         <v/>
       </c>
       <c r="B128" s="10" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>421</v>
@@ -5866,49 +5864,49 @@
         <v>424</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="str">
         <f>IF(ISNA(VLOOKUP(B129,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B129" s="10" t="s">
-        <v>357</v>
+      <c r="B129" t="s">
+        <v>393</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D129" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="str">
         <f>IF(ISNA(VLOOKUP(B130,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B130" s="10" t="s">
-        <v>363</v>
+      <c r="B130" t="s">
+        <v>396</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D130" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="str">
         <f>IF(ISNA(VLOOKUP(B131,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B131" s="10" t="s">
-        <v>366</v>
+      <c r="B131" t="s">
+        <v>399</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D131" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5917,7 +5915,7 @@
         <v/>
       </c>
       <c r="B132" s="10" t="s">
-        <v>369</v>
+        <v>474</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>421</v>
@@ -5932,13 +5930,13 @@
         <v/>
       </c>
       <c r="B133" s="10" t="s">
-        <v>372</v>
+        <v>474</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D133" t="s">
-        <v>424</v>
+        <v>480</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5947,13 +5945,13 @@
         <v/>
       </c>
       <c r="B134" s="10" t="s">
-        <v>387</v>
+        <v>474</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D134" t="s">
-        <v>424</v>
+        <v>481</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5962,13 +5960,13 @@
         <v/>
       </c>
       <c r="B135" s="10" t="s">
-        <v>390</v>
+        <v>474</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D135" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -5977,97 +5975,97 @@
         <v/>
       </c>
       <c r="B136" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D136" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A137" t="str">
+        <f>IF(ISNA(VLOOKUP(B137,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D137" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" t="str">
+        <f>IF(ISNA(VLOOKUP(B138,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B138" t="s">
         <v>402</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D136" t="s">
+      <c r="C138" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D138" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A139" t="str">
+        <f>IF(ISNA(VLOOKUP(B139,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D139" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A137" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B137,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B137" s="23" t="s">
+    <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A140" t="str">
+        <f>IF(ISNA(VLOOKUP(B140,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B140" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="C137" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D137" t="s">
+      <c r="C140" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D140" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A138" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B138,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B138" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D138" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A139" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B139,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B139" s="23" t="s">
+    <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A141" t="str">
+        <f>IF(ISNA(VLOOKUP(B141,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B141" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="C139" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D139" t="s">
+      <c r="C141" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D141" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A140" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B140,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B140" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D140" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A141" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B141,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B141" s="23" t="s">
+    <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A142" t="str">
+        <f>IF(ISNA(VLOOKUP(B142,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B142" s="10" t="s">
         <v>479</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D141" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A142" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B142,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B142" s="23" t="s">
-        <v>474</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>421</v>
@@ -6077,11 +6075,11 @@
       </c>
     </row>
     <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A143" s="22" t="str">
+      <c r="A143" t="str">
         <f>IF(ISNA(VLOOKUP(B143,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B143" s="23" t="s">
+      <c r="B143" s="10" t="s">
         <v>479</v>
       </c>
       <c r="C143" s="3" t="s">
@@ -6092,78 +6090,123 @@
       </c>
     </row>
     <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A144" s="22" t="str">
+      <c r="A144" t="str">
         <f>IF(ISNA(VLOOKUP(B144,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B144" s="23" t="s">
-        <v>474</v>
+      <c r="B144" s="10" t="s">
+        <v>479</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>421</v>
       </c>
       <c r="D144" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A145" t="str">
+        <f>IF(ISNA(VLOOKUP(B145,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D145" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" t="str">
+        <f>IF(ISNA(VLOOKUP(B146,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B146" t="s">
+        <v>405</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D146" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" t="str">
+        <f>IF(ISNA(VLOOKUP(B147,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B147" t="s">
+        <v>414</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D147" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" t="str">
+        <f>IF(ISNA(VLOOKUP(B148,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B148" t="s">
+        <v>411</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D148" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" t="str">
+        <f>IF(ISNA(VLOOKUP(B149,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B149" t="s">
+        <v>408</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D149" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" t="str">
+        <f>IF(ISNA(VLOOKUP(B150,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B150" t="s">
+        <v>417</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D150" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A151" s="22" t="str">
+        <f>IF(ISNA(VLOOKUP(B151,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B151" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D151" t="s">
         <v>482</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A145" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B145,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B145" s="23" t="s">
-        <v>479</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D145" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A146" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B146,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B146" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D146" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A147" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B147,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B147" s="23" t="s">
-        <v>479</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D147" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A148" s="22" t="str">
-        <f>IF(ISNA(VLOOKUP(B148,Definitions!B$2:B$1882,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B148" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D148" t="s">
-        <v>438</v>
       </c>
     </row>
   </sheetData>
